--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,22 +2170,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,22 +7525,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,22 +7644,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,22 +13118,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,22 +13951,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L147" t="n">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18505,7 +18505,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G155" t="n">

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI156"/>
+  <dimension ref="A1:AI161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1332,27 +1332,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46080.39583333334</v>
+        <v>46080.375</v>
       </c>
     </row>
     <row r="9">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46080.41666666666</v>
+        <v>46080.39583333334</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46080.42708333334</v>
+        <v>46080.41666666666</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46080.4375</v>
+        <v>46080.42708333334</v>
       </c>
     </row>
     <row r="12">
@@ -1808,27 +1808,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46080.44791666666</v>
+        <v>46080.4375</v>
       </c>
     </row>
     <row r="13">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46080.45833333334</v>
+        <v>46080.4375</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46080.45833333334</v>
+        <v>46080.4375</v>
       </c>
     </row>
     <row r="15">
@@ -2165,27 +2165,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46080.45833333334</v>
+        <v>46080.44791666666</v>
       </c>
     </row>
     <row r="16">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46080.46875</v>
+        <v>46080.45833333334</v>
       </c>
     </row>
     <row r="20">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46080.5</v>
+        <v>46080.45833333334</v>
       </c>
     </row>
     <row r="21">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46080.5</v>
+        <v>46080.45833333334</v>
       </c>
     </row>
     <row r="22">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46080.5</v>
+        <v>46080.45833333334</v>
       </c>
     </row>
     <row r="23">
@@ -3117,27 +3117,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46080.5</v>
+        <v>46080.46875</v>
       </c>
     </row>
     <row r="24">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46080.52083333334</v>
+        <v>46080.5</v>
       </c>
     </row>
     <row r="25">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46080.52083333334</v>
+        <v>46080.5</v>
       </c>
     </row>
     <row r="26">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46080.52083333334</v>
+        <v>46080.5</v>
       </c>
     </row>
     <row r="27">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46080.52083333334</v>
+        <v>46080.5</v>
       </c>
     </row>
     <row r="28">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46080.53125</v>
+        <v>46080.52083333334</v>
       </c>
     </row>
     <row r="29">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46080.54166666666</v>
+        <v>46080.52083333334</v>
       </c>
     </row>
     <row r="30">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>9.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46080.5625</v>
+        <v>46080.52083333334</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46080.58333333334</v>
+        <v>46080.52083333334</v>
       </c>
     </row>
     <row r="32">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>46080.58333333334</v>
+        <v>46080.53125</v>
       </c>
     </row>
     <row r="33">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4417,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
-        <v>46080.58333333334</v>
+        <v>46080.54166666666</v>
       </c>
     </row>
     <row r="34">
@@ -4426,12 +4426,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>46080.58333333334</v>
+        <v>46080.5625</v>
       </c>
     </row>
     <row r="35">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="AI50" s="3" t="n">
-        <v>46080.59375</v>
+        <v>46080.58333333334</v>
       </c>
     </row>
     <row r="51">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6559,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
-        <v>46080.60416666666</v>
+        <v>46080.58333333334</v>
       </c>
     </row>
     <row r="52">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6678,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="AI52" s="3" t="n">
-        <v>46080.60416666666</v>
+        <v>46080.58333333334</v>
       </c>
     </row>
     <row r="53">
@@ -6687,12 +6687,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
-        <v>46080.60416666666</v>
+        <v>46080.58333333334</v>
       </c>
     </row>
     <row r="54">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="AI54" s="3" t="n">
-        <v>46080.60416666666</v>
+        <v>46080.59375</v>
       </c>
     </row>
     <row r="55">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7282,12 +7282,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7392,7 +7392,7 @@
         <v>0</v>
       </c>
       <c r="AI58" s="3" t="n">
-        <v>46080.625</v>
+        <v>46080.60416666666</v>
       </c>
     </row>
     <row r="59">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7511,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="AI59" s="3" t="n">
-        <v>46080.625</v>
+        <v>46080.60416666666</v>
       </c>
     </row>
     <row r="60">
@@ -7520,27 +7520,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7630,7 +7630,7 @@
         <v>0</v>
       </c>
       <c r="AI60" s="3" t="n">
-        <v>46080.625</v>
+        <v>46080.60416666666</v>
       </c>
     </row>
     <row r="61">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7749,7 +7749,7 @@
         <v>0</v>
       </c>
       <c r="AI61" s="3" t="n">
-        <v>46080.625</v>
+        <v>46080.60416666666</v>
       </c>
     </row>
     <row r="62">
@@ -7758,12 +7758,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7868,7 +7868,7 @@
         <v>0</v>
       </c>
       <c r="AI62" s="3" t="n">
-        <v>46080.64583333334</v>
+        <v>46080.625</v>
       </c>
     </row>
     <row r="63">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7987,7 +7987,7 @@
         <v>0</v>
       </c>
       <c r="AI63" s="3" t="n">
-        <v>46080.64583333334</v>
+        <v>46080.625</v>
       </c>
     </row>
     <row r="64">
@@ -7996,27 +7996,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8106,7 +8106,7 @@
         <v>0</v>
       </c>
       <c r="AI64" s="3" t="n">
-        <v>46080.64583333334</v>
+        <v>46080.625</v>
       </c>
     </row>
     <row r="65">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="AI65" s="3" t="n">
-        <v>46080.64583333334</v>
+        <v>46080.625</v>
       </c>
     </row>
     <row r="66">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8939,7 +8939,7 @@
         <v>0</v>
       </c>
       <c r="AI71" s="3" t="n">
-        <v>46080.65625</v>
+        <v>46080.64583333334</v>
       </c>
     </row>
     <row r="72">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9058,7 +9058,7 @@
         <v>0</v>
       </c>
       <c r="AI72" s="3" t="n">
-        <v>46080.66666666666</v>
+        <v>46080.64583333334</v>
       </c>
     </row>
     <row r="73">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9177,7 +9177,7 @@
         <v>0</v>
       </c>
       <c r="AI73" s="3" t="n">
-        <v>46080.66666666666</v>
+        <v>46080.64583333334</v>
       </c>
     </row>
     <row r="74">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -9296,7 +9296,7 @@
         <v>0</v>
       </c>
       <c r="AI74" s="3" t="n">
-        <v>46080.66666666666</v>
+        <v>46080.64583333334</v>
       </c>
     </row>
     <row r="75">
@@ -9305,12 +9305,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9415,7 +9415,7 @@
         <v>0</v>
       </c>
       <c r="AI75" s="3" t="n">
-        <v>46080.66666666666</v>
+        <v>46080.65625</v>
       </c>
     </row>
     <row r="76">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11566,12 +11566,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11676,7 +11676,7 @@
         <v>0</v>
       </c>
       <c r="AI94" s="3" t="n">
-        <v>46080.67708333334</v>
+        <v>46080.66666666666</v>
       </c>
     </row>
     <row r="95">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11795,7 +11795,7 @@
         <v>0</v>
       </c>
       <c r="AI95" s="3" t="n">
-        <v>46080.67708333334</v>
+        <v>46080.66666666666</v>
       </c>
     </row>
     <row r="96">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11914,7 +11914,7 @@
         <v>0</v>
       </c>
       <c r="AI96" s="3" t="n">
-        <v>46080.6875</v>
+        <v>46080.66666666666</v>
       </c>
     </row>
     <row r="97">
@@ -11923,12 +11923,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12033,7 +12033,7 @@
         <v>0</v>
       </c>
       <c r="AI97" s="3" t="n">
-        <v>46080.6875</v>
+        <v>46080.66666666666</v>
       </c>
     </row>
     <row r="98">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12152,7 +12152,7 @@
         <v>0</v>
       </c>
       <c r="AI98" s="3" t="n">
-        <v>46080.6875</v>
+        <v>46080.67708333334</v>
       </c>
     </row>
     <row r="99">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12271,7 +12271,7 @@
         <v>0</v>
       </c>
       <c r="AI99" s="3" t="n">
-        <v>46080.6875</v>
+        <v>46080.67708333334</v>
       </c>
     </row>
     <row r="100">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12756,27 +12756,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12866,7 +12866,7 @@
         <v>0</v>
       </c>
       <c r="AI104" s="3" t="n">
-        <v>46080.69791666666</v>
+        <v>46080.6875</v>
       </c>
     </row>
     <row r="105">
@@ -12875,27 +12875,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12985,7 +12985,7 @@
         <v>0</v>
       </c>
       <c r="AI105" s="3" t="n">
-        <v>46080.69791666666</v>
+        <v>46080.6875</v>
       </c>
     </row>
     <row r="106">
@@ -12994,12 +12994,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13104,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="AI106" s="3" t="n">
-        <v>46080.69791666666</v>
+        <v>46080.6875</v>
       </c>
     </row>
     <row r="107">
@@ -13113,12 +13113,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13223,7 +13223,7 @@
         <v>0</v>
       </c>
       <c r="AI107" s="3" t="n">
-        <v>46080.69791666666</v>
+        <v>46080.6875</v>
       </c>
     </row>
     <row r="108">
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14303,27 +14303,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14413,7 +14413,7 @@
         <v>0</v>
       </c>
       <c r="AI117" s="3" t="n">
-        <v>46080.70833333334</v>
+        <v>46080.69791666666</v>
       </c>
     </row>
     <row r="118">
@@ -14422,27 +14422,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14532,7 +14532,7 @@
         <v>0</v>
       </c>
       <c r="AI118" s="3" t="n">
-        <v>46080.70833333334</v>
+        <v>46080.69791666666</v>
       </c>
     </row>
     <row r="119">
@@ -14541,27 +14541,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14651,7 +14651,7 @@
         <v>0</v>
       </c>
       <c r="AI119" s="3" t="n">
-        <v>46080.70833333334</v>
+        <v>46080.69791666666</v>
       </c>
     </row>
     <row r="120">
@@ -14660,27 +14660,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14770,7 +14770,7 @@
         <v>0</v>
       </c>
       <c r="AI120" s="3" t="n">
-        <v>46080.70833333334</v>
+        <v>46080.69791666666</v>
       </c>
     </row>
     <row r="121">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15017,12 +15017,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15127,7 +15127,7 @@
         <v>0</v>
       </c>
       <c r="AI123" s="3" t="n">
-        <v>46080.73958333334</v>
+        <v>46080.70833333334</v>
       </c>
     </row>
     <row r="124">
@@ -15136,27 +15136,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15246,7 +15246,7 @@
         <v>0</v>
       </c>
       <c r="AI124" s="3" t="n">
-        <v>46080.75</v>
+        <v>46080.70833333334</v>
       </c>
     </row>
     <row r="125">
@@ -15255,27 +15255,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15365,7 +15365,7 @@
         <v>0</v>
       </c>
       <c r="AI125" s="3" t="n">
-        <v>46080.75</v>
+        <v>46080.70833333334</v>
       </c>
     </row>
     <row r="126">
@@ -15374,12 +15374,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15484,7 +15484,7 @@
         <v>0</v>
       </c>
       <c r="AI126" s="3" t="n">
-        <v>46080.79166666666</v>
+        <v>46080.70833333334</v>
       </c>
     </row>
     <row r="127">
@@ -15493,12 +15493,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15603,7 +15603,7 @@
         <v>0</v>
       </c>
       <c r="AI127" s="3" t="n">
-        <v>46080.79166666666</v>
+        <v>46080.73958333334</v>
       </c>
     </row>
     <row r="128">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15722,7 +15722,7 @@
         <v>0</v>
       </c>
       <c r="AI128" s="3" t="n">
-        <v>46080.85416666666</v>
+        <v>46080.75</v>
       </c>
     </row>
     <row r="129">
@@ -15731,27 +15731,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AI129" s="3" t="n">
-        <v>46080.85416666666</v>
+        <v>46080.75</v>
       </c>
     </row>
     <row r="130">
@@ -15850,27 +15850,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15960,7 +15960,7 @@
         <v>0</v>
       </c>
       <c r="AI130" s="3" t="n">
-        <v>46080.875</v>
+        <v>46080.75</v>
       </c>
     </row>
     <row r="131">
@@ -15969,12 +15969,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16079,7 +16079,7 @@
         <v>0</v>
       </c>
       <c r="AI131" s="3" t="n">
-        <v>46080.875</v>
+        <v>46080.79166666666</v>
       </c>
     </row>
     <row r="132">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16198,7 +16198,7 @@
         <v>0</v>
       </c>
       <c r="AI132" s="3" t="n">
-        <v>46080.875</v>
+        <v>46080.79166666666</v>
       </c>
     </row>
     <row r="133">
@@ -16207,27 +16207,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16317,7 +16317,7 @@
         <v>0</v>
       </c>
       <c r="AI133" s="3" t="n">
-        <v>46080.875</v>
+        <v>46080.85416666666</v>
       </c>
     </row>
     <row r="134">
@@ -16326,27 +16326,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16436,7 +16436,7 @@
         <v>0</v>
       </c>
       <c r="AI134" s="3" t="n">
-        <v>46080.875</v>
+        <v>46080.85416666666</v>
       </c>
     </row>
     <row r="135">
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L144" t="n">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18944,116 +18944,711 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>FAP</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Tekstilac Odžaci</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="n">
+        <v>0</v>
+      </c>
+      <c r="T156" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" t="n">
+        <v>0</v>
+      </c>
+      <c r="V156" t="n">
+        <v>0</v>
+      </c>
+      <c r="W156" t="n">
+        <v>0</v>
+      </c>
+      <c r="X156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI156" s="3" t="n">
+        <v>46080.875</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Loznica</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Grafičar</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="n">
+        <v>0</v>
+      </c>
+      <c r="V157" t="n">
+        <v>0</v>
+      </c>
+      <c r="W157" t="n">
+        <v>0</v>
+      </c>
+      <c r="X157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI157" s="3" t="n">
+        <v>46080.875</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>USM Khenchela</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Oued Akbou</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="n">
+        <v>0</v>
+      </c>
+      <c r="T158" t="n">
+        <v>0</v>
+      </c>
+      <c r="U158" t="n">
+        <v>0</v>
+      </c>
+      <c r="V158" t="n">
+        <v>0</v>
+      </c>
+      <c r="W158" t="n">
+        <v>0</v>
+      </c>
+      <c r="X158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="3" t="n">
+        <v>46080.875</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>MB Rouisset</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>ASO Chlef</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" t="n">
+        <v>0</v>
+      </c>
+      <c r="U159" t="n">
+        <v>0</v>
+      </c>
+      <c r="V159" t="n">
+        <v>0</v>
+      </c>
+      <c r="W159" t="n">
+        <v>0</v>
+      </c>
+      <c r="X159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI159" s="3" t="n">
+        <v>46080.875</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Radnički Niš</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Javor Ivanjica</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="n">
+        <v>0</v>
+      </c>
+      <c r="T160" t="n">
+        <v>0</v>
+      </c>
+      <c r="U160" t="n">
+        <v>0</v>
+      </c>
+      <c r="V160" t="n">
+        <v>0</v>
+      </c>
+      <c r="W160" t="n">
+        <v>0</v>
+      </c>
+      <c r="X160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI160" s="3" t="n">
+        <v>46080.875</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="E161" t="inlineStr">
         <is>
           <t>Técnico Universitario</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>Orense SC</t>
         </is>
       </c>
-      <c r="G156" t="n">
-        <v>0</v>
-      </c>
-      <c r="H156" t="n">
-        <v>0</v>
-      </c>
-      <c r="I156" t="n">
-        <v>0</v>
-      </c>
-      <c r="J156" t="n">
-        <v>0</v>
-      </c>
-      <c r="K156" t="inlineStr">
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L156" t="n">
-        <v>0</v>
-      </c>
-      <c r="M156" t="n">
-        <v>0</v>
-      </c>
-      <c r="N156" t="n">
-        <v>0</v>
-      </c>
-      <c r="O156" t="n">
-        <v>0</v>
-      </c>
-      <c r="P156" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
-      <c r="R156" t="n">
-        <v>0</v>
-      </c>
-      <c r="S156" t="n">
-        <v>0</v>
-      </c>
-      <c r="T156" t="n">
-        <v>0</v>
-      </c>
-      <c r="U156" t="n">
-        <v>0</v>
-      </c>
-      <c r="V156" t="n">
-        <v>0</v>
-      </c>
-      <c r="W156" t="n">
-        <v>0</v>
-      </c>
-      <c r="X156" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y156" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI156" s="3" t="n">
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" t="n">
+        <v>0</v>
+      </c>
+      <c r="U161" t="n">
+        <v>0</v>
+      </c>
+      <c r="V161" t="n">
+        <v>0</v>
+      </c>
+      <c r="W161" t="n">
+        <v>0</v>
+      </c>
+      <c r="X161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI161" s="3" t="n">
         <v>46080.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI161"/>
+  <dimension ref="A1:AI168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46080.39583333334</v>
+        <v>46080.375</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46080.41666666666</v>
+        <v>46080.375</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46080.42708333334</v>
+        <v>46080.375</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46080.4375</v>
+        <v>46080.375</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46080.4375</v>
+        <v>46080.375</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46080.4375</v>
+        <v>46080.375</v>
       </c>
     </row>
     <row r="15">
@@ -2165,27 +2165,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46080.44791666666</v>
+        <v>46080.375</v>
       </c>
     </row>
     <row r="16">
@@ -2284,27 +2284,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46080.45833333334</v>
+        <v>46080.39583333334</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46080.45833333334</v>
+        <v>46080.41666666666</v>
       </c>
     </row>
     <row r="18">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.32</v>
+        <v>3.14</v>
       </c>
       <c r="M18" t="n">
-        <v>2.69</v>
+        <v>3.13</v>
       </c>
       <c r="N18" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46080.45833333334</v>
+        <v>46080.42708333334</v>
       </c>
     </row>
     <row r="19">
@@ -2641,27 +2641,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46080.45833333334</v>
+        <v>46080.4375</v>
       </c>
     </row>
     <row r="20">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46080.45833333334</v>
+        <v>46080.4375</v>
       </c>
     </row>
     <row r="21">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46080.45833333334</v>
+        <v>46080.4375</v>
       </c>
     </row>
     <row r="22">
@@ -2998,27 +2998,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46080.45833333334</v>
+        <v>46080.44791666666</v>
       </c>
     </row>
     <row r="23">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46080.46875</v>
+        <v>46080.45833333334</v>
       </c>
     </row>
     <row r="24">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46080.5</v>
+        <v>46080.45833333334</v>
       </c>
     </row>
     <row r="25">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46080.5</v>
+        <v>46080.45833333334</v>
       </c>
     </row>
     <row r="26">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46080.5</v>
+        <v>46080.45833333334</v>
       </c>
     </row>
     <row r="27">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46080.5</v>
+        <v>46080.45833333334</v>
       </c>
     </row>
     <row r="28">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46080.52083333334</v>
+        <v>46080.45833333334</v>
       </c>
     </row>
     <row r="29">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46080.52083333334</v>
+        <v>46080.45833333334</v>
       </c>
     </row>
     <row r="30">
@@ -3950,27 +3950,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46080.52083333334</v>
+        <v>46080.46875</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46080.52083333334</v>
+        <v>46080.5</v>
       </c>
     </row>
     <row r="32">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>46080.53125</v>
+        <v>46080.5</v>
       </c>
     </row>
     <row r="33">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4417,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
-        <v>46080.54166666666</v>
+        <v>46080.5</v>
       </c>
     </row>
     <row r="34">
@@ -4426,12 +4426,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>9.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>46080.5625</v>
+        <v>46080.5</v>
       </c>
     </row>
     <row r="35">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>46080.58333333334</v>
+        <v>46080.52083333334</v>
       </c>
     </row>
     <row r="36">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4774,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>46080.58333333334</v>
+        <v>46080.52083333334</v>
       </c>
     </row>
     <row r="37">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>46080.58333333334</v>
+        <v>46080.52083333334</v>
       </c>
     </row>
     <row r="38">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46080.58333333334</v>
+        <v>46080.52083333334</v>
       </c>
     </row>
     <row r="39">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5131,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>46080.58333333334</v>
+        <v>46080.53125</v>
       </c>
     </row>
     <row r="40">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5250,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>46080.58333333334</v>
+        <v>46080.54166666666</v>
       </c>
     </row>
     <row r="41">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5369,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
-        <v>46080.58333333334</v>
+        <v>46080.5625</v>
       </c>
     </row>
     <row r="42">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="AI54" s="3" t="n">
-        <v>46080.59375</v>
+        <v>46080.58333333334</v>
       </c>
     </row>
     <row r="55">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7035,7 +7035,7 @@
         <v>0</v>
       </c>
       <c r="AI55" s="3" t="n">
-        <v>46080.60416666666</v>
+        <v>46080.58333333334</v>
       </c>
     </row>
     <row r="56">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7154,7 +7154,7 @@
         <v>0</v>
       </c>
       <c r="AI56" s="3" t="n">
-        <v>46080.60416666666</v>
+        <v>46080.58333333334</v>
       </c>
     </row>
     <row r="57">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7273,7 +7273,7 @@
         <v>0</v>
       </c>
       <c r="AI57" s="3" t="n">
-        <v>46080.60416666666</v>
+        <v>46080.58333333334</v>
       </c>
     </row>
     <row r="58">
@@ -7282,12 +7282,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7392,7 +7392,7 @@
         <v>0</v>
       </c>
       <c r="AI58" s="3" t="n">
-        <v>46080.60416666666</v>
+        <v>46080.58333333334</v>
       </c>
     </row>
     <row r="59">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7511,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="AI59" s="3" t="n">
-        <v>46080.60416666666</v>
+        <v>46080.58333333334</v>
       </c>
     </row>
     <row r="60">
@@ -7520,12 +7520,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7630,7 +7630,7 @@
         <v>0</v>
       </c>
       <c r="AI60" s="3" t="n">
-        <v>46080.60416666666</v>
+        <v>46080.58333333334</v>
       </c>
     </row>
     <row r="61">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7749,7 +7749,7 @@
         <v>0</v>
       </c>
       <c r="AI61" s="3" t="n">
-        <v>46080.60416666666</v>
+        <v>46080.59375</v>
       </c>
     </row>
     <row r="62">
@@ -7758,12 +7758,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7868,7 +7868,7 @@
         <v>0</v>
       </c>
       <c r="AI62" s="3" t="n">
-        <v>46080.625</v>
+        <v>46080.60416666666</v>
       </c>
     </row>
     <row r="63">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7987,7 +7987,7 @@
         <v>0</v>
       </c>
       <c r="AI63" s="3" t="n">
-        <v>46080.625</v>
+        <v>46080.60416666666</v>
       </c>
     </row>
     <row r="64">
@@ -7996,27 +7996,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8106,7 +8106,7 @@
         <v>0</v>
       </c>
       <c r="AI64" s="3" t="n">
-        <v>46080.625</v>
+        <v>46080.60416666666</v>
       </c>
     </row>
     <row r="65">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="AI65" s="3" t="n">
-        <v>46080.625</v>
+        <v>46080.60416666666</v>
       </c>
     </row>
     <row r="66">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8344,7 +8344,7 @@
         <v>0</v>
       </c>
       <c r="AI66" s="3" t="n">
-        <v>46080.64583333334</v>
+        <v>46080.60416666666</v>
       </c>
     </row>
     <row r="67">
@@ -8353,12 +8353,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8463,7 +8463,7 @@
         <v>0</v>
       </c>
       <c r="AI67" s="3" t="n">
-        <v>46080.64583333334</v>
+        <v>46080.60416666666</v>
       </c>
     </row>
     <row r="68">
@@ -8472,12 +8472,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8582,7 +8582,7 @@
         <v>0</v>
       </c>
       <c r="AI68" s="3" t="n">
-        <v>46080.64583333334</v>
+        <v>46080.60416666666</v>
       </c>
     </row>
     <row r="69">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8701,7 +8701,7 @@
         <v>0</v>
       </c>
       <c r="AI69" s="3" t="n">
-        <v>46080.64583333334</v>
+        <v>46080.625</v>
       </c>
     </row>
     <row r="70">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8820,7 +8820,7 @@
         <v>0</v>
       </c>
       <c r="AI70" s="3" t="n">
-        <v>46080.64583333334</v>
+        <v>46080.625</v>
       </c>
     </row>
     <row r="71">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8939,7 +8939,7 @@
         <v>0</v>
       </c>
       <c r="AI71" s="3" t="n">
-        <v>46080.64583333334</v>
+        <v>46080.625</v>
       </c>
     </row>
     <row r="72">
@@ -8948,27 +8948,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9058,7 +9058,7 @@
         <v>0</v>
       </c>
       <c r="AI72" s="3" t="n">
-        <v>46080.64583333334</v>
+        <v>46080.625</v>
       </c>
     </row>
     <row r="73">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -9305,12 +9305,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9415,7 +9415,7 @@
         <v>0</v>
       </c>
       <c r="AI75" s="3" t="n">
-        <v>46080.65625</v>
+        <v>46080.64583333334</v>
       </c>
     </row>
     <row r="76">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9534,7 +9534,7 @@
         <v>0</v>
       </c>
       <c r="AI76" s="3" t="n">
-        <v>46080.66666666666</v>
+        <v>46080.64583333334</v>
       </c>
     </row>
     <row r="77">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9653,7 +9653,7 @@
         <v>0</v>
       </c>
       <c r="AI77" s="3" t="n">
-        <v>46080.66666666666</v>
+        <v>46080.64583333334</v>
       </c>
     </row>
     <row r="78">
@@ -9662,12 +9662,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -9772,7 +9772,7 @@
         <v>0</v>
       </c>
       <c r="AI78" s="3" t="n">
-        <v>46080.66666666666</v>
+        <v>46080.64583333334</v>
       </c>
     </row>
     <row r="79">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AI79" s="3" t="n">
-        <v>46080.66666666666</v>
+        <v>46080.64583333334</v>
       </c>
     </row>
     <row r="80">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10010,7 +10010,7 @@
         <v>0</v>
       </c>
       <c r="AI80" s="3" t="n">
-        <v>46080.66666666666</v>
+        <v>46080.64583333334</v>
       </c>
     </row>
     <row r="81">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10129,7 +10129,7 @@
         <v>0</v>
       </c>
       <c r="AI81" s="3" t="n">
-        <v>46080.66666666666</v>
+        <v>46080.64583333334</v>
       </c>
     </row>
     <row r="82">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10248,7 +10248,7 @@
         <v>0</v>
       </c>
       <c r="AI82" s="3" t="n">
-        <v>46080.66666666666</v>
+        <v>46080.65625</v>
       </c>
     </row>
     <row r="83">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12152,7 +12152,7 @@
         <v>0</v>
       </c>
       <c r="AI98" s="3" t="n">
-        <v>46080.67708333334</v>
+        <v>46080.66666666666</v>
       </c>
     </row>
     <row r="99">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12271,7 +12271,7 @@
         <v>0</v>
       </c>
       <c r="AI99" s="3" t="n">
-        <v>46080.67708333334</v>
+        <v>46080.66666666666</v>
       </c>
     </row>
     <row r="100">
@@ -12280,12 +12280,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12390,7 +12390,7 @@
         <v>0</v>
       </c>
       <c r="AI100" s="3" t="n">
-        <v>46080.6875</v>
+        <v>46080.66666666666</v>
       </c>
     </row>
     <row r="101">
@@ -12399,12 +12399,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12509,7 +12509,7 @@
         <v>0</v>
       </c>
       <c r="AI101" s="3" t="n">
-        <v>46080.6875</v>
+        <v>46080.66666666666</v>
       </c>
     </row>
     <row r="102">
@@ -12518,12 +12518,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12628,7 +12628,7 @@
         <v>0</v>
       </c>
       <c r="AI102" s="3" t="n">
-        <v>46080.6875</v>
+        <v>46080.66666666666</v>
       </c>
     </row>
     <row r="103">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12747,7 +12747,7 @@
         <v>0</v>
       </c>
       <c r="AI103" s="3" t="n">
-        <v>46080.6875</v>
+        <v>46080.66666666666</v>
       </c>
     </row>
     <row r="104">
@@ -12756,12 +12756,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12866,7 +12866,7 @@
         <v>0</v>
       </c>
       <c r="AI104" s="3" t="n">
-        <v>46080.6875</v>
+        <v>46080.66666666666</v>
       </c>
     </row>
     <row r="105">
@@ -12875,12 +12875,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12985,7 +12985,7 @@
         <v>0</v>
       </c>
       <c r="AI105" s="3" t="n">
-        <v>46080.6875</v>
+        <v>46080.67708333334</v>
       </c>
     </row>
     <row r="106">
@@ -12994,12 +12994,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13104,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="AI106" s="3" t="n">
-        <v>46080.6875</v>
+        <v>46080.67708333334</v>
       </c>
     </row>
     <row r="107">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13232,27 +13232,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13342,7 +13342,7 @@
         <v>0</v>
       </c>
       <c r="AI108" s="3" t="n">
-        <v>46080.69791666666</v>
+        <v>46080.6875</v>
       </c>
     </row>
     <row r="109">
@@ -13351,12 +13351,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13461,7 +13461,7 @@
         <v>0</v>
       </c>
       <c r="AI109" s="3" t="n">
-        <v>46080.69791666666</v>
+        <v>46080.6875</v>
       </c>
     </row>
     <row r="110">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13580,7 +13580,7 @@
         <v>0</v>
       </c>
       <c r="AI110" s="3" t="n">
-        <v>46080.69791666666</v>
+        <v>46080.6875</v>
       </c>
     </row>
     <row r="111">
@@ -13589,27 +13589,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13699,7 +13699,7 @@
         <v>0</v>
       </c>
       <c r="AI111" s="3" t="n">
-        <v>46080.69791666666</v>
+        <v>46080.6875</v>
       </c>
     </row>
     <row r="112">
@@ -13708,12 +13708,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13818,7 +13818,7 @@
         <v>0</v>
       </c>
       <c r="AI112" s="3" t="n">
-        <v>46080.69791666666</v>
+        <v>46080.6875</v>
       </c>
     </row>
     <row r="113">
@@ -13827,27 +13827,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13937,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="AI113" s="3" t="n">
-        <v>46080.69791666666</v>
+        <v>46080.6875</v>
       </c>
     </row>
     <row r="114">
@@ -13946,27 +13946,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14056,7 +14056,7 @@
         <v>0</v>
       </c>
       <c r="AI114" s="3" t="n">
-        <v>46080.69791666666</v>
+        <v>46080.6875</v>
       </c>
     </row>
     <row r="115">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14779,12 +14779,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14889,7 +14889,7 @@
         <v>0</v>
       </c>
       <c r="AI121" s="3" t="n">
-        <v>46080.70833333334</v>
+        <v>46080.69791666666</v>
       </c>
     </row>
     <row r="122">
@@ -14898,27 +14898,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="AI122" s="3" t="n">
-        <v>46080.70833333334</v>
+        <v>46080.69791666666</v>
       </c>
     </row>
     <row r="123">
@@ -15017,12 +15017,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15127,7 +15127,7 @@
         <v>0</v>
       </c>
       <c r="AI123" s="3" t="n">
-        <v>46080.70833333334</v>
+        <v>46080.69791666666</v>
       </c>
     </row>
     <row r="124">
@@ -15136,27 +15136,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15246,7 +15246,7 @@
         <v>0</v>
       </c>
       <c r="AI124" s="3" t="n">
-        <v>46080.70833333334</v>
+        <v>46080.69791666666</v>
       </c>
     </row>
     <row r="125">
@@ -15255,12 +15255,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15365,7 +15365,7 @@
         <v>0</v>
       </c>
       <c r="AI125" s="3" t="n">
-        <v>46080.70833333334</v>
+        <v>46080.69791666666</v>
       </c>
     </row>
     <row r="126">
@@ -15374,27 +15374,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15484,7 +15484,7 @@
         <v>0</v>
       </c>
       <c r="AI126" s="3" t="n">
-        <v>46080.70833333334</v>
+        <v>46080.69791666666</v>
       </c>
     </row>
     <row r="127">
@@ -15493,12 +15493,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15603,7 +15603,7 @@
         <v>0</v>
       </c>
       <c r="AI127" s="3" t="n">
-        <v>46080.73958333334</v>
+        <v>46080.69791666666</v>
       </c>
     </row>
     <row r="128">
@@ -15612,27 +15612,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15722,7 +15722,7 @@
         <v>0</v>
       </c>
       <c r="AI128" s="3" t="n">
-        <v>46080.75</v>
+        <v>46080.70833333334</v>
       </c>
     </row>
     <row r="129">
@@ -15731,12 +15731,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AI129" s="3" t="n">
-        <v>46080.75</v>
+        <v>46080.70833333334</v>
       </c>
     </row>
     <row r="130">
@@ -15850,27 +15850,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15960,7 +15960,7 @@
         <v>0</v>
       </c>
       <c r="AI130" s="3" t="n">
-        <v>46080.75</v>
+        <v>46080.70833333334</v>
       </c>
     </row>
     <row r="131">
@@ -15969,12 +15969,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16079,7 +16079,7 @@
         <v>0</v>
       </c>
       <c r="AI131" s="3" t="n">
-        <v>46080.79166666666</v>
+        <v>46080.70833333334</v>
       </c>
     </row>
     <row r="132">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16198,7 +16198,7 @@
         <v>0</v>
       </c>
       <c r="AI132" s="3" t="n">
-        <v>46080.79166666666</v>
+        <v>46080.70833333334</v>
       </c>
     </row>
     <row r="133">
@@ -16207,12 +16207,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16317,7 +16317,7 @@
         <v>0</v>
       </c>
       <c r="AI133" s="3" t="n">
-        <v>46080.85416666666</v>
+        <v>46080.70833333334</v>
       </c>
     </row>
     <row r="134">
@@ -16326,27 +16326,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16436,7 +16436,7 @@
         <v>0</v>
       </c>
       <c r="AI134" s="3" t="n">
-        <v>46080.85416666666</v>
+        <v>46080.73958333334</v>
       </c>
     </row>
     <row r="135">
@@ -16445,27 +16445,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16555,7 +16555,7 @@
         <v>0</v>
       </c>
       <c r="AI135" s="3" t="n">
-        <v>46080.875</v>
+        <v>46080.75</v>
       </c>
     </row>
     <row r="136">
@@ -16564,27 +16564,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16674,7 +16674,7 @@
         <v>0</v>
       </c>
       <c r="AI136" s="3" t="n">
-        <v>46080.875</v>
+        <v>46080.75</v>
       </c>
     </row>
     <row r="137">
@@ -16683,27 +16683,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16793,7 +16793,7 @@
         <v>0</v>
       </c>
       <c r="AI137" s="3" t="n">
-        <v>46080.875</v>
+        <v>46080.75</v>
       </c>
     </row>
     <row r="138">
@@ -16802,12 +16802,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16912,7 +16912,7 @@
         <v>0</v>
       </c>
       <c r="AI138" s="3" t="n">
-        <v>46080.875</v>
+        <v>46080.79166666666</v>
       </c>
     </row>
     <row r="139">
@@ -16921,12 +16921,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17031,7 +17031,7 @@
         <v>0</v>
       </c>
       <c r="AI139" s="3" t="n">
-        <v>46080.875</v>
+        <v>46080.79166666666</v>
       </c>
     </row>
     <row r="140">
@@ -17040,27 +17040,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17150,7 +17150,7 @@
         <v>0</v>
       </c>
       <c r="AI140" s="3" t="n">
-        <v>46080.875</v>
+        <v>46080.85416666666</v>
       </c>
     </row>
     <row r="141">
@@ -17159,27 +17159,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17269,7 +17269,7 @@
         <v>0</v>
       </c>
       <c r="AI141" s="3" t="n">
-        <v>46080.875</v>
+        <v>46080.85416666666</v>
       </c>
     </row>
     <row r="142">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L144" t="n">
@@ -17640,22 +17640,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18624,7 +18624,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19539,116 +19539,949 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>ES Sétif</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>ES Mostaganem</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" t="n">
+        <v>0</v>
+      </c>
+      <c r="U161" t="n">
+        <v>0</v>
+      </c>
+      <c r="V161" t="n">
+        <v>0</v>
+      </c>
+      <c r="W161" t="n">
+        <v>0</v>
+      </c>
+      <c r="X161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI161" s="3" t="n">
+        <v>46080.875</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Dinamo Jug</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Mačva Šabac</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="n">
+        <v>0</v>
+      </c>
+      <c r="V162" t="n">
+        <v>0</v>
+      </c>
+      <c r="W162" t="n">
+        <v>0</v>
+      </c>
+      <c r="X162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI162" s="3" t="n">
+        <v>46080.875</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>USM Khenchela</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Oued Akbou</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="n">
+        <v>0</v>
+      </c>
+      <c r="V163" t="n">
+        <v>0</v>
+      </c>
+      <c r="W163" t="n">
+        <v>0</v>
+      </c>
+      <c r="X163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI163" s="3" t="n">
+        <v>46080.875</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>MB Rouisset</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>ASO Chlef</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" t="n">
+        <v>0</v>
+      </c>
+      <c r="U164" t="n">
+        <v>0</v>
+      </c>
+      <c r="V164" t="n">
+        <v>0</v>
+      </c>
+      <c r="W164" t="n">
+        <v>0</v>
+      </c>
+      <c r="X164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI164" s="3" t="n">
+        <v>46080.875</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Radnik Bijeljina</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Velež</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="n">
+        <v>0</v>
+      </c>
+      <c r="T165" t="n">
+        <v>0</v>
+      </c>
+      <c r="U165" t="n">
+        <v>0</v>
+      </c>
+      <c r="V165" t="n">
+        <v>0</v>
+      </c>
+      <c r="W165" t="n">
+        <v>0</v>
+      </c>
+      <c r="X165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI165" s="3" t="n">
+        <v>46080.875</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Partizan</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>OFK Beograd</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" t="n">
+        <v>0</v>
+      </c>
+      <c r="U166" t="n">
+        <v>0</v>
+      </c>
+      <c r="V166" t="n">
+        <v>0</v>
+      </c>
+      <c r="W166" t="n">
+        <v>0</v>
+      </c>
+      <c r="X166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI166" s="3" t="n">
+        <v>46080.875</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Semendrija 1924</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Kabel Novi Sad</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="n">
+        <v>0</v>
+      </c>
+      <c r="V167" t="n">
+        <v>0</v>
+      </c>
+      <c r="W167" t="n">
+        <v>0</v>
+      </c>
+      <c r="X167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI167" s="3" t="n">
+        <v>46080.875</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
+      <c r="C168" t="inlineStr">
         <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D168" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="E168" t="inlineStr">
         <is>
           <t>Técnico Universitario</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
+      <c r="F168" t="inlineStr">
         <is>
           <t>Orense SC</t>
         </is>
       </c>
-      <c r="G161" t="n">
-        <v>0</v>
-      </c>
-      <c r="H161" t="n">
-        <v>0</v>
-      </c>
-      <c r="I161" t="n">
-        <v>0</v>
-      </c>
-      <c r="J161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K161" t="inlineStr">
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L161" t="n">
-        <v>0</v>
-      </c>
-      <c r="M161" t="n">
-        <v>0</v>
-      </c>
-      <c r="N161" t="n">
-        <v>0</v>
-      </c>
-      <c r="O161" t="n">
-        <v>0</v>
-      </c>
-      <c r="P161" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0</v>
-      </c>
-      <c r="S161" t="n">
-        <v>0</v>
-      </c>
-      <c r="T161" t="n">
-        <v>0</v>
-      </c>
-      <c r="U161" t="n">
-        <v>0</v>
-      </c>
-      <c r="V161" t="n">
-        <v>0</v>
-      </c>
-      <c r="W161" t="n">
-        <v>0</v>
-      </c>
-      <c r="X161" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y161" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI161" s="3" t="n">
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="n">
+        <v>0</v>
+      </c>
+      <c r="T168" t="n">
+        <v>0</v>
+      </c>
+      <c r="U168" t="n">
+        <v>0</v>
+      </c>
+      <c r="V168" t="n">
+        <v>0</v>
+      </c>
+      <c r="W168" t="n">
+        <v>0</v>
+      </c>
+      <c r="X168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI168" s="3" t="n">
         <v>46080.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.32</v>
+        <v>2.26</v>
       </c>
       <c r="M25" t="n">
-        <v>2.69</v>
+        <v>3.03</v>
       </c>
       <c r="N25" t="n">
-        <v>2.08</v>
+        <v>3.65</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,22 +3598,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.26</v>
+        <v>4.32</v>
       </c>
       <c r="M29" t="n">
-        <v>3.03</v>
+        <v>2.69</v>
       </c>
       <c r="N29" t="n">
-        <v>3.65</v>
+        <v>2.08</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,22 +8834,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,22 +8953,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,22 +15022,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,22 +15260,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,22 +15498,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,22 +15736,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,22 +16212,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,22 +17640,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18505,7 +18505,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18624,7 +18624,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,22 +19782,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G167" t="n">

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3598,22 +3598,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,22 +3717,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.32</v>
+        <v>2.26</v>
       </c>
       <c r="M29" t="n">
-        <v>2.69</v>
+        <v>3.03</v>
       </c>
       <c r="N29" t="n">
-        <v>2.08</v>
+        <v>3.65</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,22 +8596,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,22 +8834,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,22 +14427,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,22 +15736,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,22 +16212,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,22 +16569,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18505,7 +18505,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,22 +19068,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,22 +19782,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19814,7 +19814,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G167" t="n">

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.32</v>
+        <v>2.26</v>
       </c>
       <c r="M23" t="n">
-        <v>2.69</v>
+        <v>3.03</v>
       </c>
       <c r="N23" t="n">
-        <v>2.08</v>
+        <v>3.65</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,22 +15022,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,22 +16212,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,22 +16569,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,22 +16688,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17791,7 +17791,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,22 +18949,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,22 +19068,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19814,7 +19814,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G167" t="n">

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,22 +3479,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3717,22 +3717,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,22 +8596,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,22 +8834,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,22 +15022,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,22 +16093,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,22 +16688,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17791,7 +17791,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,22 +18949,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,22 +19663,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G167" t="n">

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,22 +3717,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.52</v>
+        <v>1.91</v>
       </c>
       <c r="M49" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="N49" t="n">
-        <v>2.44</v>
+        <v>3.48</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,22 +8596,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8834,22 +8834,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,22 +14427,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,22 +14784,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,22 +15022,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,22 +16569,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,22 +19663,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,22 +20139,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G167" t="n">

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI168"/>
+  <dimension ref="A1:AI167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46080.375</v>
+        <v>46080.35416666666</v>
       </c>
     </row>
     <row r="7">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2284,27 +2284,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46080.39583333334</v>
+        <v>46080.375</v>
       </c>
     </row>
     <row r="17">
@@ -2403,27 +2403,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46080.41666666666</v>
+        <v>46080.39583333334</v>
       </c>
     </row>
     <row r="18">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46080.42708333334</v>
+        <v>46080.41666666666</v>
       </c>
     </row>
     <row r="19">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46080.4375</v>
+        <v>46080.42708333334</v>
       </c>
     </row>
     <row r="20">
@@ -2998,27 +2998,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46080.44791666666</v>
+        <v>46080.4375</v>
       </c>
     </row>
     <row r="23">
@@ -3117,27 +3117,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46080.45833333334</v>
+        <v>46080.44791666666</v>
       </c>
     </row>
     <row r="24">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,22 +3717,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3950,27 +3950,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46080.46875</v>
+        <v>46080.45833333334</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46080.5</v>
+        <v>46080.45833333334</v>
       </c>
     </row>
     <row r="32">
@@ -4188,27 +4188,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>46080.5</v>
+        <v>46080.46875</v>
       </c>
     </row>
     <row r="33">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>46080.52083333334</v>
+        <v>46080.5</v>
       </c>
     </row>
     <row r="36">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4774,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>46080.52083333334</v>
+        <v>46080.5</v>
       </c>
     </row>
     <row r="37">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5131,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>46080.53125</v>
+        <v>46080.52083333334</v>
       </c>
     </row>
     <row r="40">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5250,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>46080.54166666666</v>
+        <v>46080.52083333334</v>
       </c>
     </row>
     <row r="41">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.48</v>
+        <v>3.79</v>
       </c>
       <c r="M41" t="n">
-        <v>4.28</v>
+        <v>3.44</v>
       </c>
       <c r="N41" t="n">
-        <v>9.550000000000001</v>
+        <v>1.93</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5369,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
-        <v>46080.5625</v>
+        <v>46080.53125</v>
       </c>
     </row>
     <row r="42">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5488,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
-        <v>46080.58333333334</v>
+        <v>46080.54166666666</v>
       </c>
     </row>
     <row r="43">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
-        <v>46080.58333333334</v>
+        <v>46080.5625</v>
       </c>
     </row>
     <row r="44">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7749,7 +7749,7 @@
         <v>0</v>
       </c>
       <c r="AI61" s="3" t="n">
-        <v>46080.59375</v>
+        <v>46080.58333333334</v>
       </c>
     </row>
     <row r="62">
@@ -7758,12 +7758,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7868,7 +7868,7 @@
         <v>0</v>
       </c>
       <c r="AI62" s="3" t="n">
-        <v>46080.60416666666</v>
+        <v>46080.58333333334</v>
       </c>
     </row>
     <row r="63">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7987,7 +7987,7 @@
         <v>0</v>
       </c>
       <c r="AI63" s="3" t="n">
-        <v>46080.60416666666</v>
+        <v>46080.59375</v>
       </c>
     </row>
     <row r="64">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8591,27 +8591,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8701,7 +8701,7 @@
         <v>0</v>
       </c>
       <c r="AI69" s="3" t="n">
-        <v>46080.625</v>
+        <v>46080.60416666666</v>
       </c>
     </row>
     <row r="70">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8820,7 +8820,7 @@
         <v>0</v>
       </c>
       <c r="AI70" s="3" t="n">
-        <v>46080.625</v>
+        <v>46080.60416666666</v>
       </c>
     </row>
     <row r="71">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9177,7 +9177,7 @@
         <v>0</v>
       </c>
       <c r="AI73" s="3" t="n">
-        <v>46080.64583333334</v>
+        <v>46080.625</v>
       </c>
     </row>
     <row r="74">
@@ -9186,27 +9186,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9296,7 +9296,7 @@
         <v>0</v>
       </c>
       <c r="AI74" s="3" t="n">
-        <v>46080.64583333334</v>
+        <v>46080.625</v>
       </c>
     </row>
     <row r="75">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10248,7 +10248,7 @@
         <v>0</v>
       </c>
       <c r="AI82" s="3" t="n">
-        <v>46080.65625</v>
+        <v>46080.64583333334</v>
       </c>
     </row>
     <row r="83">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10367,7 +10367,7 @@
         <v>0</v>
       </c>
       <c r="AI83" s="3" t="n">
-        <v>46080.66666666666</v>
+        <v>46080.64583333334</v>
       </c>
     </row>
     <row r="84">
@@ -10376,12 +10376,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10486,7 +10486,7 @@
         <v>0</v>
       </c>
       <c r="AI84" s="3" t="n">
-        <v>46080.66666666666</v>
+        <v>46080.65625</v>
       </c>
     </row>
     <row r="85">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12875,12 +12875,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12985,7 +12985,7 @@
         <v>0</v>
       </c>
       <c r="AI105" s="3" t="n">
-        <v>46080.67708333334</v>
+        <v>46080.66666666666</v>
       </c>
     </row>
     <row r="106">
@@ -12994,12 +12994,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13104,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="AI106" s="3" t="n">
-        <v>46080.67708333334</v>
+        <v>46080.66666666666</v>
       </c>
     </row>
     <row r="107">
@@ -13113,12 +13113,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13223,7 +13223,7 @@
         <v>0</v>
       </c>
       <c r="AI107" s="3" t="n">
-        <v>46080.6875</v>
+        <v>46080.67708333334</v>
       </c>
     </row>
     <row r="108">
@@ -13232,12 +13232,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13342,7 +13342,7 @@
         <v>0</v>
       </c>
       <c r="AI108" s="3" t="n">
-        <v>46080.6875</v>
+        <v>46080.67708333334</v>
       </c>
     </row>
     <row r="109">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14065,27 +14065,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14175,7 +14175,7 @@
         <v>0</v>
       </c>
       <c r="AI115" s="3" t="n">
-        <v>46080.69791666666</v>
+        <v>46080.6875</v>
       </c>
     </row>
     <row r="116">
@@ -14184,27 +14184,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14294,7 +14294,7 @@
         <v>0</v>
       </c>
       <c r="AI116" s="3" t="n">
-        <v>46080.69791666666</v>
+        <v>46080.6875</v>
       </c>
     </row>
     <row r="117">
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,22 +14784,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15612,27 +15612,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15722,7 +15722,7 @@
         <v>0</v>
       </c>
       <c r="AI128" s="3" t="n">
-        <v>46080.70833333334</v>
+        <v>46080.69791666666</v>
       </c>
     </row>
     <row r="129">
@@ -15731,27 +15731,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AI129" s="3" t="n">
-        <v>46080.70833333334</v>
+        <v>46080.69791666666</v>
       </c>
     </row>
     <row r="130">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,22 +16093,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,22 +16212,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16436,7 +16436,7 @@
         <v>0</v>
       </c>
       <c r="AI134" s="3" t="n">
-        <v>46080.73958333334</v>
+        <v>46080.70833333334</v>
       </c>
     </row>
     <row r="135">
@@ -16445,27 +16445,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16555,7 +16555,7 @@
         <v>0</v>
       </c>
       <c r="AI135" s="3" t="n">
-        <v>46080.75</v>
+        <v>46080.70833333334</v>
       </c>
     </row>
     <row r="136">
@@ -16564,12 +16564,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16674,7 +16674,7 @@
         <v>0</v>
       </c>
       <c r="AI136" s="3" t="n">
-        <v>46080.75</v>
+        <v>46080.73958333334</v>
       </c>
     </row>
     <row r="137">
@@ -16802,27 +16802,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16912,7 +16912,7 @@
         <v>0</v>
       </c>
       <c r="AI138" s="3" t="n">
-        <v>46080.79166666666</v>
+        <v>46080.75</v>
       </c>
     </row>
     <row r="139">
@@ -16921,12 +16921,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17031,7 +17031,7 @@
         <v>0</v>
       </c>
       <c r="AI139" s="3" t="n">
-        <v>46080.79166666666</v>
+        <v>46080.75</v>
       </c>
     </row>
     <row r="140">
@@ -17040,27 +17040,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17150,7 +17150,7 @@
         <v>0</v>
       </c>
       <c r="AI140" s="3" t="n">
-        <v>46080.85416666666</v>
+        <v>46080.79166666666</v>
       </c>
     </row>
     <row r="141">
@@ -17159,27 +17159,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17269,7 +17269,7 @@
         <v>0</v>
       </c>
       <c r="AI141" s="3" t="n">
-        <v>46080.85416666666</v>
+        <v>46080.79166666666</v>
       </c>
     </row>
     <row r="142">
@@ -17278,27 +17278,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17388,7 +17388,7 @@
         <v>0</v>
       </c>
       <c r="AI142" s="3" t="n">
-        <v>46080.875</v>
+        <v>46080.85416666666</v>
       </c>
     </row>
     <row r="143">
@@ -17397,27 +17397,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17507,7 +17507,7 @@
         <v>0</v>
       </c>
       <c r="AI143" s="3" t="n">
-        <v>46080.875</v>
+        <v>46080.85416666666</v>
       </c>
     </row>
     <row r="144">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,22 +18949,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19457,7 +19457,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,22 +20139,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20253,27 +20253,27 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20363,125 +20363,6 @@
         <v>0</v>
       </c>
       <c r="AI167" s="3" t="n">
-        <v>46080.875</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="n">
-        <v>46080</v>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Técnico Universitario</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Orense SC</t>
-        </is>
-      </c>
-      <c r="G168" t="n">
-        <v>0</v>
-      </c>
-      <c r="H168" t="n">
-        <v>0</v>
-      </c>
-      <c r="I168" t="n">
-        <v>0</v>
-      </c>
-      <c r="J168" t="n">
-        <v>0</v>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L168" t="n">
-        <v>0</v>
-      </c>
-      <c r="M168" t="n">
-        <v>0</v>
-      </c>
-      <c r="N168" t="n">
-        <v>0</v>
-      </c>
-      <c r="O168" t="n">
-        <v>0</v>
-      </c>
-      <c r="P168" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
-      <c r="R168" t="n">
-        <v>0</v>
-      </c>
-      <c r="S168" t="n">
-        <v>0</v>
-      </c>
-      <c r="T168" t="n">
-        <v>0</v>
-      </c>
-      <c r="U168" t="n">
-        <v>0</v>
-      </c>
-      <c r="V168" t="n">
-        <v>0</v>
-      </c>
-      <c r="W168" t="n">
-        <v>0</v>
-      </c>
-      <c r="X168" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y168" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI168" s="3" t="n">
         <v>46080.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,22 +3955,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,22 +9072,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,22 +14546,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,22 +15022,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>7.09</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -16212,22 +16212,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -18116,22 +18116,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,22 +18949,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19457,7 +19457,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19814,7 +19814,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G165" t="n">

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,22 +3955,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.52</v>
+        <v>1.91</v>
       </c>
       <c r="M58" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="N58" t="n">
-        <v>2.44</v>
+        <v>3.48</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8564,10 +8564,10 @@
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,22 +9072,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,22 +14546,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="M123" t="n">
-        <v>3.74</v>
+        <v>4.5</v>
       </c>
       <c r="N123" t="n">
-        <v>4.85</v>
+        <v>7.09</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,22 +15260,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="M129" t="n">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="N129" t="n">
-        <v>7.09</v>
+        <v>4.85</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,22 +18116,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19576,7 +19576,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19814,7 +19814,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,22 +20020,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G166" t="n">

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,22 +4074,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,22 +9072,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9461,17 +9461,17 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>5.07</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="M93" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N93" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.56</v>
+        <v>2.56</v>
       </c>
       <c r="M97" t="n">
-        <v>4</v>
+        <v>3.04</v>
       </c>
       <c r="N97" t="n">
-        <v>5.18</v>
+        <v>2.84</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>3.03</v>
+        <v>1.56</v>
       </c>
       <c r="M103" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N103" t="n">
-        <v>2.17</v>
+        <v>5.18</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="M117" t="n">
-        <v>3.25</v>
+        <v>3.66</v>
       </c>
       <c r="N117" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,22 +14546,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>3.31</v>
+        <v>2.56</v>
       </c>
       <c r="M119" t="n">
-        <v>3.04</v>
+        <v>3.21</v>
       </c>
       <c r="N119" t="n">
-        <v>2.29</v>
+        <v>2.9</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>7.09</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,22 +15260,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.7</v>
+        <v>1.42</v>
       </c>
       <c r="M125" t="n">
-        <v>3.66</v>
+        <v>4.5</v>
       </c>
       <c r="N125" t="n">
-        <v>2.7</v>
+        <v>7.09</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="M126" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="N126" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,22 +16212,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,22 +18711,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18862,7 +18862,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19576,7 +19576,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,22 +20020,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G166" t="n">

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,22 +4074,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8088,10 +8088,10 @@
         <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8564,10 +8564,10 @@
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9072,22 +9072,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9342,17 +9342,17 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>5.07</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M80" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="N80" t="n">
-        <v>3.58</v>
+        <v>3.86</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10175,17 +10175,17 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.55</v>
+        <v>1.56</v>
       </c>
       <c r="M106" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N106" t="n">
-        <v>2.7</v>
+        <v>5.18</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="M117" t="n">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="N117" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,22 +14546,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.56</v>
+        <v>1.69</v>
       </c>
       <c r="M119" t="n">
-        <v>3.21</v>
+        <v>3.74</v>
       </c>
       <c r="N119" t="n">
-        <v>2.9</v>
+        <v>4.85</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3.31</v>
+        <v>1.42</v>
       </c>
       <c r="M121" t="n">
-        <v>3.04</v>
+        <v>4.5</v>
       </c>
       <c r="N121" t="n">
-        <v>2.29</v>
+        <v>7.09</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>7.09</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,22 +15498,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,22 +15617,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="M128" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N128" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,22 +15736,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,22 +18711,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18743,7 +18743,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18862,7 +18862,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L155" t="n">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,22 +19068,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G166" t="n">

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.32</v>
+        <v>2.75</v>
       </c>
       <c r="M64" t="n">
-        <v>3.65</v>
+        <v>2.55</v>
       </c>
       <c r="N64" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8088,10 +8088,10 @@
         <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8564,10 +8564,10 @@
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,22 +9072,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.82</v>
+        <v>2.01</v>
       </c>
       <c r="M81" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N81" t="n">
-        <v>2.4</v>
+        <v>3.58</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10294,17 +10294,17 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.55</v>
+        <v>1.56</v>
       </c>
       <c r="M101" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N101" t="n">
-        <v>2.7</v>
+        <v>5.18</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="M113" t="n">
-        <v>3.4</v>
+        <v>3.71</v>
       </c>
       <c r="N113" t="n">
-        <v>2.43</v>
+        <v>3.04</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="M117" t="n">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="N117" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.42</v>
+        <v>2.34</v>
       </c>
       <c r="M121" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="N121" t="n">
-        <v>7.09</v>
+        <v>2.57</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,22 +15022,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>3.31</v>
+        <v>2.5</v>
       </c>
       <c r="M123" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="N123" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,22 +15498,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.56</v>
+        <v>1.42</v>
       </c>
       <c r="M127" t="n">
-        <v>3.21</v>
+        <v>4.5</v>
       </c>
       <c r="N127" t="n">
-        <v>2.9</v>
+        <v>7.09</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,22 +15617,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="M128" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="N128" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="M129" t="n">
-        <v>3.66</v>
+        <v>3.21</v>
       </c>
       <c r="N129" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,22 +16212,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18743,7 +18743,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,22 +19068,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,22 +19425,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G166" t="n">

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
+        <v>3.74</v>
       </c>
       <c r="N56" t="n">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,22 +9072,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.6</v>
+        <v>2.82</v>
       </c>
       <c r="M82" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N82" t="n">
-        <v>5.07</v>
+        <v>2.4</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10294,17 +10294,17 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>3.03</v>
+        <v>2.52</v>
       </c>
       <c r="M88" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="N88" t="n">
-        <v>2.17</v>
+        <v>2.83</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="M95" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N95" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.52</v>
+        <v>2.97</v>
       </c>
       <c r="M97" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="N97" t="n">
-        <v>2.83</v>
+        <v>2.36</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.56</v>
+        <v>1.56</v>
       </c>
       <c r="M98" t="n">
-        <v>3.04</v>
+        <v>4</v>
       </c>
       <c r="N98" t="n">
-        <v>2.84</v>
+        <v>5.18</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="M103" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N103" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>3.43</v>
+        <v>2.44</v>
       </c>
       <c r="M105" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="N105" t="n">
-        <v>2.36</v>
+        <v>2.98</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="M117" t="n">
-        <v>3.66</v>
+        <v>3.25</v>
       </c>
       <c r="N117" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,22 +14427,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.34</v>
+        <v>3.31</v>
       </c>
       <c r="M121" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="N121" t="n">
-        <v>2.57</v>
+        <v>2.29</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>3.31</v>
+        <v>2.25</v>
       </c>
       <c r="M126" t="n">
-        <v>3.04</v>
+        <v>3.24</v>
       </c>
       <c r="N126" t="n">
-        <v>2.29</v>
+        <v>2.89</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>7.09</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,22 +15617,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="M128" t="n">
-        <v>3.24</v>
+        <v>3.66</v>
       </c>
       <c r="N128" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,22 +15736,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.56</v>
+        <v>1.42</v>
       </c>
       <c r="M129" t="n">
-        <v>3.21</v>
+        <v>4.5</v>
       </c>
       <c r="N129" t="n">
-        <v>2.9</v>
+        <v>7.09</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,22 +18711,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,22 +19425,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20052,7 +20052,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G166" t="n">

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.32</v>
+        <v>2.26</v>
       </c>
       <c r="M29" t="n">
-        <v>2.69</v>
+        <v>3.03</v>
       </c>
       <c r="N29" t="n">
-        <v>2.08</v>
+        <v>3.65</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8564,10 +8564,10 @@
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8683,10 +8683,10 @@
         <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -8834,22 +8834,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>5.07</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10175,17 +10175,17 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.89</v>
+        <v>2.82</v>
       </c>
       <c r="M83" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="N83" t="n">
-        <v>3.86</v>
+        <v>2.4</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="M88" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="N88" t="n">
-        <v>2.83</v>
+        <v>2.98</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.55</v>
+        <v>1.56</v>
       </c>
       <c r="M91" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N91" t="n">
-        <v>2.7</v>
+        <v>5.18</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>3.03</v>
+        <v>3.43</v>
       </c>
       <c r="M103" t="n">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="N103" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,22 +15498,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,22 +15617,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.7</v>
+        <v>1.42</v>
       </c>
       <c r="M128" t="n">
-        <v>3.66</v>
+        <v>4.5</v>
       </c>
       <c r="N128" t="n">
-        <v>2.7</v>
+        <v>7.09</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.42</v>
+        <v>3.31</v>
       </c>
       <c r="M129" t="n">
-        <v>4.5</v>
+        <v>3.04</v>
       </c>
       <c r="N129" t="n">
-        <v>7.09</v>
+        <v>2.29</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15974,22 +15974,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>4.62</v>
+        <v>2.32</v>
       </c>
       <c r="M132" t="n">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="N132" t="n">
-        <v>1.86</v>
+        <v>2.85</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AB132" t="n">
         <v>1.95</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,22 +18711,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L159" t="n">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,22 +19901,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20052,7 +20052,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G166" t="n">

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.32</v>
+        <v>2.26</v>
       </c>
       <c r="M31" t="n">
-        <v>2.69</v>
+        <v>3.03</v>
       </c>
       <c r="N31" t="n">
-        <v>2.08</v>
+        <v>3.65</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.52</v>
+        <v>2.21</v>
       </c>
       <c r="M50" t="n">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="N50" t="n">
-        <v>2.44</v>
+        <v>3.06</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8088,10 +8088,10 @@
         <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8683,10 +8683,10 @@
         <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,22 +8834,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>5.07</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.89</v>
+        <v>2.82</v>
       </c>
       <c r="M80" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="N80" t="n">
-        <v>3.86</v>
+        <v>2.4</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10175,17 +10175,17 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.55</v>
+        <v>3.03</v>
       </c>
       <c r="M86" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N86" t="n">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="M91" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="N91" t="n">
-        <v>5.18</v>
+        <v>2.98</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="M118" t="n">
-        <v>3.21</v>
+        <v>3.66</v>
       </c>
       <c r="N118" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>7.09</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -15022,22 +15022,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="M124" t="n">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="N124" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,22 +15260,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>7.09</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15974,22 +15974,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,22 +16093,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18029,7 +18029,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L148" t="n">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L159" t="n">
@@ -19425,22 +19425,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,22 +19901,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G166" t="n">

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,22 +3955,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.32</v>
+        <v>2.75</v>
       </c>
       <c r="M64" t="n">
-        <v>3.65</v>
+        <v>2.55</v>
       </c>
       <c r="N64" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8088,10 +8088,10 @@
         <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.07</v>
+        <v>2.32</v>
       </c>
       <c r="M68" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N68" t="n">
-        <v>2.16</v>
+        <v>2.72</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,16 +8558,16 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,22 +8834,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="M75" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="N75" t="n">
-        <v>5.07</v>
+        <v>3.86</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9461,17 +9461,17 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10175,17 +10175,17 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.97</v>
+        <v>2.56</v>
       </c>
       <c r="M85" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="N85" t="n">
-        <v>2.36</v>
+        <v>2.84</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.03</v>
+        <v>2.44</v>
       </c>
       <c r="M86" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N86" t="n">
-        <v>2.17</v>
+        <v>2.98</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.44</v>
+        <v>2.97</v>
       </c>
       <c r="M91" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N91" t="n">
-        <v>2.98</v>
+        <v>2.36</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.56</v>
+        <v>3.03</v>
       </c>
       <c r="M92" t="n">
-        <v>3.04</v>
+        <v>3.45</v>
       </c>
       <c r="N92" t="n">
-        <v>2.84</v>
+        <v>2.17</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14427,22 +14427,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>7.09</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>7.09</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.69</v>
+        <v>2.56</v>
       </c>
       <c r="M122" t="n">
-        <v>3.74</v>
+        <v>3.21</v>
       </c>
       <c r="N122" t="n">
-        <v>4.85</v>
+        <v>2.9</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,22 +15022,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="M123" t="n">
-        <v>3.24</v>
+        <v>3.66</v>
       </c>
       <c r="N123" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="M124" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N124" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,22 +15260,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="M125" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="N125" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.56</v>
+        <v>3.31</v>
       </c>
       <c r="M126" t="n">
-        <v>3.21</v>
+        <v>3.04</v>
       </c>
       <c r="N126" t="n">
-        <v>2.9</v>
+        <v>2.29</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.84</v>
+        <v>2.32</v>
       </c>
       <c r="M130" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N130" t="n">
-        <v>4.29</v>
+        <v>2.85</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,22 +16093,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>4.62</v>
+        <v>1.84</v>
       </c>
       <c r="M133" t="n">
-        <v>3.84</v>
+        <v>3.4</v>
       </c>
       <c r="N133" t="n">
-        <v>1.86</v>
+        <v>4.29</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,22 +17997,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18029,7 +18029,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,22 +19425,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19695,7 +19695,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G166" t="n">

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="M75" t="n">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="N75" t="n">
-        <v>3.86</v>
+        <v>3.27</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.6</v>
+        <v>2.82</v>
       </c>
       <c r="M77" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N77" t="n">
-        <v>5.07</v>
+        <v>2.4</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9818,17 +9818,17 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10175,17 +10175,17 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.03</v>
+        <v>2.55</v>
       </c>
       <c r="M92" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N92" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.56</v>
+        <v>2.52</v>
       </c>
       <c r="M99" t="n">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="N99" t="n">
-        <v>5.18</v>
+        <v>2.83</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.55</v>
+        <v>2.97</v>
       </c>
       <c r="M100" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N100" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,22 +14546,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="M119" t="n">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="N119" t="n">
-        <v>2.57</v>
+        <v>2.9</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,22 +15022,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.7</v>
+        <v>3.31</v>
       </c>
       <c r="M123" t="n">
-        <v>3.66</v>
+        <v>3.04</v>
       </c>
       <c r="N123" t="n">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="M124" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="N124" t="n">
-        <v>2.5</v>
+        <v>3.19</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,22 +15260,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>3.31</v>
+        <v>2.5</v>
       </c>
       <c r="M126" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="N126" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,22 +15498,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.84</v>
+        <v>4.62</v>
       </c>
       <c r="M133" t="n">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="N133" t="n">
-        <v>4.29</v>
+        <v>1.86</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>4.62</v>
+        <v>1.84</v>
       </c>
       <c r="M135" t="n">
-        <v>3.84</v>
+        <v>3.4</v>
       </c>
       <c r="N135" t="n">
-        <v>1.86</v>
+        <v>4.29</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,22 +17997,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,22 +18711,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19695,7 +19695,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19814,7 +19814,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G166" t="n">

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI167"/>
+  <dimension ref="A1:AI162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1689,27 +1689,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46080.375</v>
+        <v>46080.39583333334</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46080.375</v>
+        <v>46080.41666666666</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46080.375</v>
+        <v>46080.41666666666</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46080.375</v>
+        <v>46080.42708333334</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46080.375</v>
+        <v>46080.4375</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46080.375</v>
+        <v>46080.4375</v>
       </c>
     </row>
     <row r="17">
@@ -2403,27 +2403,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46080.39583333334</v>
+        <v>46080.4375</v>
       </c>
     </row>
     <row r="18">
@@ -2522,27 +2522,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46080.41666666666</v>
+        <v>46080.44791666666</v>
       </c>
     </row>
     <row r="19">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46080.42708333334</v>
+        <v>46080.45833333334</v>
       </c>
     </row>
     <row r="20">
@@ -2760,27 +2760,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46080.4375</v>
+        <v>46080.45833333334</v>
       </c>
     </row>
     <row r="21">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46080.4375</v>
+        <v>46080.45833333334</v>
       </c>
     </row>
     <row r="22">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46080.4375</v>
+        <v>46080.45833333334</v>
       </c>
     </row>
     <row r="23">
@@ -3117,27 +3117,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46080.44791666666</v>
+        <v>46080.45833333334</v>
       </c>
     </row>
     <row r="24">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3593,27 +3593,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46080.45833333334</v>
+        <v>46080.46875</v>
       </c>
     </row>
     <row r="28">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46080.45833333334</v>
+        <v>46080.5</v>
       </c>
     </row>
     <row r="29">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46080.45833333334</v>
+        <v>46080.5</v>
       </c>
     </row>
     <row r="30">
@@ -3950,27 +3950,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46080.45833333334</v>
+        <v>46080.5</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46080.45833333334</v>
+        <v>46080.5</v>
       </c>
     </row>
     <row r="32">
@@ -4188,27 +4188,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>46080.46875</v>
+        <v>46080.52083333334</v>
       </c>
     </row>
     <row r="33">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4417,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
-        <v>46080.5</v>
+        <v>46080.52083333334</v>
       </c>
     </row>
     <row r="34">
@@ -4426,12 +4426,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>46080.5</v>
+        <v>46080.52083333334</v>
       </c>
     </row>
     <row r="35">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>46080.5</v>
+        <v>46080.52083333334</v>
       </c>
     </row>
     <row r="36">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.4</v>
+        <v>3.79</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="N36" t="n">
-        <v>3.28</v>
+        <v>1.93</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>46080.5</v>
+        <v>46080.53125</v>
       </c>
     </row>
     <row r="37">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>46080.52083333334</v>
+        <v>46080.54166666666</v>
       </c>
     </row>
     <row r="38">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46080.52083333334</v>
+        <v>46080.5625</v>
       </c>
     </row>
     <row r="39">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5131,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>46080.52083333334</v>
+        <v>46080.58333333334</v>
       </c>
     </row>
     <row r="40">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5250,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>46080.52083333334</v>
+        <v>46080.58333333334</v>
       </c>
     </row>
     <row r="41">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5369,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
-        <v>46080.53125</v>
+        <v>46080.58333333334</v>
       </c>
     </row>
     <row r="42">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5488,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
-        <v>46080.54166666666</v>
+        <v>46080.58333333334</v>
       </c>
     </row>
     <row r="43">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="M43" t="n">
-        <v>4.28</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>9.550000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
-        <v>46080.5625</v>
+        <v>46080.58333333334</v>
       </c>
     </row>
     <row r="44">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="M51" t="n">
-        <v>3</v>
+        <v>3.74</v>
       </c>
       <c r="N51" t="n">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.91</v>
+        <v>2.52</v>
       </c>
       <c r="M57" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="N57" t="n">
-        <v>3.48</v>
+        <v>2.44</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7282,12 +7282,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7392,7 +7392,7 @@
         <v>0</v>
       </c>
       <c r="AI58" s="3" t="n">
-        <v>46080.58333333334</v>
+        <v>46080.59375</v>
       </c>
     </row>
     <row r="59">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7511,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="AI59" s="3" t="n">
-        <v>46080.58333333334</v>
+        <v>46080.60416666666</v>
       </c>
     </row>
     <row r="60">
@@ -7520,12 +7520,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7630,7 +7630,7 @@
         <v>0</v>
       </c>
       <c r="AI60" s="3" t="n">
-        <v>46080.58333333334</v>
+        <v>46080.60416666666</v>
       </c>
     </row>
     <row r="61">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7749,7 +7749,7 @@
         <v>0</v>
       </c>
       <c r="AI61" s="3" t="n">
-        <v>46080.58333333334</v>
+        <v>46080.60416666666</v>
       </c>
     </row>
     <row r="62">
@@ -7758,12 +7758,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -7868,7 +7868,7 @@
         <v>0</v>
       </c>
       <c r="AI62" s="3" t="n">
-        <v>46080.58333333334</v>
+        <v>46080.60416666666</v>
       </c>
     </row>
     <row r="63">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7987,7 +7987,7 @@
         <v>0</v>
       </c>
       <c r="AI63" s="3" t="n">
-        <v>46080.59375</v>
+        <v>46080.60416666666</v>
       </c>
     </row>
     <row r="64">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8344,7 +8344,7 @@
         <v>0</v>
       </c>
       <c r="AI66" s="3" t="n">
-        <v>46080.60416666666</v>
+        <v>46080.625</v>
       </c>
     </row>
     <row r="67">
@@ -8353,12 +8353,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8463,7 +8463,7 @@
         <v>0</v>
       </c>
       <c r="AI67" s="3" t="n">
-        <v>46080.60416666666</v>
+        <v>46080.625</v>
       </c>
     </row>
     <row r="68">
@@ -8472,27 +8472,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8564,10 +8564,10 @@
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -8582,7 +8582,7 @@
         <v>0</v>
       </c>
       <c r="AI68" s="3" t="n">
-        <v>46080.60416666666</v>
+        <v>46080.625</v>
       </c>
     </row>
     <row r="69">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.07</v>
+        <v>1.54</v>
       </c>
       <c r="M69" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N69" t="n">
-        <v>2.16</v>
+        <v>6.29</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8701,7 +8701,7 @@
         <v>0</v>
       </c>
       <c r="AI69" s="3" t="n">
-        <v>46080.60416666666</v>
+        <v>46080.625</v>
       </c>
     </row>
     <row r="70">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8820,7 +8820,7 @@
         <v>0</v>
       </c>
       <c r="AI70" s="3" t="n">
-        <v>46080.60416666666</v>
+        <v>46080.64583333334</v>
       </c>
     </row>
     <row r="71">
@@ -8829,27 +8829,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8939,7 +8939,7 @@
         <v>0</v>
       </c>
       <c r="AI71" s="3" t="n">
-        <v>46080.625</v>
+        <v>46080.64583333334</v>
       </c>
     </row>
     <row r="72">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9058,7 +9058,7 @@
         <v>0</v>
       </c>
       <c r="AI72" s="3" t="n">
-        <v>46080.625</v>
+        <v>46080.64583333334</v>
       </c>
     </row>
     <row r="73">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9177,7 +9177,7 @@
         <v>0</v>
       </c>
       <c r="AI73" s="3" t="n">
-        <v>46080.625</v>
+        <v>46080.64583333334</v>
       </c>
     </row>
     <row r="74">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9223,17 +9223,17 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9296,7 +9296,7 @@
         <v>0</v>
       </c>
       <c r="AI74" s="3" t="n">
-        <v>46080.625</v>
+        <v>46080.64583333334</v>
       </c>
     </row>
     <row r="75">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.82</v>
+        <v>2.11</v>
       </c>
       <c r="M77" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="N77" t="n">
-        <v>2.4</v>
+        <v>3.27</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9781,12 +9781,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9818,17 +9818,17 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AI79" s="3" t="n">
-        <v>46080.64583333334</v>
+        <v>46080.65625</v>
       </c>
     </row>
     <row r="80">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
         <v>0</v>
       </c>
       <c r="AI80" s="3" t="n">
-        <v>46080.64583333334</v>
+        <v>46080.66666666666</v>
       </c>
     </row>
     <row r="81">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.6</v>
+        <v>2.97</v>
       </c>
       <c r="M81" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N81" t="n">
-        <v>5.07</v>
+        <v>2.36</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10129,7 +10129,7 @@
         <v>0</v>
       </c>
       <c r="AI81" s="3" t="n">
-        <v>46080.64583333334</v>
+        <v>46080.66666666666</v>
       </c>
     </row>
     <row r="82">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.89</v>
+        <v>1.56</v>
       </c>
       <c r="M82" t="n">
-        <v>3.22</v>
+        <v>4</v>
       </c>
       <c r="N82" t="n">
-        <v>3.86</v>
+        <v>5.18</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10248,7 +10248,7 @@
         <v>0</v>
       </c>
       <c r="AI82" s="3" t="n">
-        <v>46080.64583333334</v>
+        <v>46080.66666666666</v>
       </c>
     </row>
     <row r="83">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10367,7 +10367,7 @@
         <v>0</v>
       </c>
       <c r="AI83" s="3" t="n">
-        <v>46080.64583333334</v>
+        <v>46080.66666666666</v>
       </c>
     </row>
     <row r="84">
@@ -10376,12 +10376,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.16</v>
+        <v>3.03</v>
       </c>
       <c r="M84" t="n">
-        <v>8.050000000000001</v>
+        <v>3.45</v>
       </c>
       <c r="N84" t="n">
-        <v>21</v>
+        <v>2.17</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10486,7 +10486,7 @@
         <v>0</v>
       </c>
       <c r="AI84" s="3" t="n">
-        <v>46080.65625</v>
+        <v>46080.66666666666</v>
       </c>
     </row>
     <row r="85">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3.03</v>
+        <v>2.56</v>
       </c>
       <c r="M90" t="n">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="N90" t="n">
-        <v>2.17</v>
+        <v>2.84</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="M92" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="N92" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12518,12 +12518,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12628,7 +12628,7 @@
         <v>0</v>
       </c>
       <c r="AI102" s="3" t="n">
-        <v>46080.66666666666</v>
+        <v>46080.67708333334</v>
       </c>
     </row>
     <row r="103">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.44</v>
+        <v>1.62</v>
       </c>
       <c r="M103" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N103" t="n">
-        <v>2.98</v>
+        <v>4.77</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12747,7 +12747,7 @@
         <v>0</v>
       </c>
       <c r="AI103" s="3" t="n">
-        <v>46080.66666666666</v>
+        <v>46080.67708333334</v>
       </c>
     </row>
     <row r="104">
@@ -12756,12 +12756,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12866,7 +12866,7 @@
         <v>0</v>
       </c>
       <c r="AI104" s="3" t="n">
-        <v>46080.66666666666</v>
+        <v>46080.6875</v>
       </c>
     </row>
     <row r="105">
@@ -12875,12 +12875,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12985,7 +12985,7 @@
         <v>0</v>
       </c>
       <c r="AI105" s="3" t="n">
-        <v>46080.66666666666</v>
+        <v>46080.6875</v>
       </c>
     </row>
     <row r="106">
@@ -12994,12 +12994,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13104,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="AI106" s="3" t="n">
-        <v>46080.66666666666</v>
+        <v>46080.6875</v>
       </c>
     </row>
     <row r="107">
@@ -13113,12 +13113,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13223,7 +13223,7 @@
         <v>0</v>
       </c>
       <c r="AI107" s="3" t="n">
-        <v>46080.67708333334</v>
+        <v>46080.6875</v>
       </c>
     </row>
     <row r="108">
@@ -13232,12 +13232,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13342,7 +13342,7 @@
         <v>0</v>
       </c>
       <c r="AI108" s="3" t="n">
-        <v>46080.67708333334</v>
+        <v>46080.6875</v>
       </c>
     </row>
     <row r="109">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13708,12 +13708,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="M112" t="n">
-        <v>3.71</v>
+        <v>3.25</v>
       </c>
       <c r="N112" t="n">
-        <v>3.04</v>
+        <v>2.5</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13818,7 +13818,7 @@
         <v>0</v>
       </c>
       <c r="AI112" s="3" t="n">
-        <v>46080.6875</v>
+        <v>46080.69791666666</v>
       </c>
     </row>
     <row r="113">
@@ -13827,27 +13827,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13937,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="AI113" s="3" t="n">
-        <v>46080.6875</v>
+        <v>46080.69791666666</v>
       </c>
     </row>
     <row r="114">
@@ -13946,27 +13946,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="M114" t="n">
         <v>3.4</v>
       </c>
       <c r="N114" t="n">
-        <v>2.43</v>
+        <v>2.57</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14056,7 +14056,7 @@
         <v>0</v>
       </c>
       <c r="AI114" s="3" t="n">
-        <v>46080.6875</v>
+        <v>46080.69791666666</v>
       </c>
     </row>
     <row r="115">
@@ -14065,27 +14065,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>7.09</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14175,7 +14175,7 @@
         <v>0</v>
       </c>
       <c r="AI115" s="3" t="n">
-        <v>46080.6875</v>
+        <v>46080.69791666666</v>
       </c>
     </row>
     <row r="116">
@@ -14184,27 +14184,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14294,7 +14294,7 @@
         <v>0</v>
       </c>
       <c r="AI116" s="3" t="n">
-        <v>46080.6875</v>
+        <v>46080.69791666666</v>
       </c>
     </row>
     <row r="117">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="M117" t="n">
-        <v>3.66</v>
+        <v>3.21</v>
       </c>
       <c r="N117" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.25</v>
+        <v>3.31</v>
       </c>
       <c r="M118" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="N118" t="n">
-        <v>2.89</v>
+        <v>2.29</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,22 +14546,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="M120" t="n">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="N120" t="n">
-        <v>7.09</v>
+        <v>4.85</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="M121" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="N121" t="n">
-        <v>2.57</v>
+        <v>3.19</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,22 +15022,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.08</v>
+        <v>2.7</v>
       </c>
       <c r="M124" t="n">
-        <v>3.28</v>
+        <v>3.66</v>
       </c>
       <c r="N124" t="n">
-        <v>3.19</v>
+        <v>2.7</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15255,27 +15255,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15365,7 +15365,7 @@
         <v>0</v>
       </c>
       <c r="AI125" s="3" t="n">
-        <v>46080.69791666666</v>
+        <v>46080.70833333334</v>
       </c>
     </row>
     <row r="126">
@@ -15374,12 +15374,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="M126" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N126" t="n">
-        <v>2.5</v>
+        <v>4.29</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15484,7 +15484,7 @@
         <v>0</v>
       </c>
       <c r="AI126" s="3" t="n">
-        <v>46080.69791666666</v>
+        <v>46080.70833333334</v>
       </c>
     </row>
     <row r="127">
@@ -15493,27 +15493,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15603,7 +15603,7 @@
         <v>0</v>
       </c>
       <c r="AI127" s="3" t="n">
-        <v>46080.69791666666</v>
+        <v>46080.70833333334</v>
       </c>
     </row>
     <row r="128">
@@ -15612,27 +15612,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15722,7 +15722,7 @@
         <v>0</v>
       </c>
       <c r="AI128" s="3" t="n">
-        <v>46080.69791666666</v>
+        <v>46080.70833333334</v>
       </c>
     </row>
     <row r="129">
@@ -15731,27 +15731,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.69</v>
+        <v>4.62</v>
       </c>
       <c r="M129" t="n">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="N129" t="n">
-        <v>4.85</v>
+        <v>1.86</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AI129" s="3" t="n">
-        <v>46080.69791666666</v>
+        <v>46080.70833333334</v>
       </c>
     </row>
     <row r="130">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15969,12 +15969,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16079,7 +16079,7 @@
         <v>0</v>
       </c>
       <c r="AI131" s="3" t="n">
-        <v>46080.70833333334</v>
+        <v>46080.73958333334</v>
       </c>
     </row>
     <row r="132">
@@ -16088,27 +16088,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16198,7 +16198,7 @@
         <v>0</v>
       </c>
       <c r="AI132" s="3" t="n">
-        <v>46080.70833333334</v>
+        <v>46080.75</v>
       </c>
     </row>
     <row r="133">
@@ -16207,27 +16207,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16317,7 +16317,7 @@
         <v>0</v>
       </c>
       <c r="AI133" s="3" t="n">
-        <v>46080.70833333334</v>
+        <v>46080.75</v>
       </c>
     </row>
     <row r="134">
@@ -16326,27 +16326,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16436,7 +16436,7 @@
         <v>0</v>
       </c>
       <c r="AI134" s="3" t="n">
-        <v>46080.70833333334</v>
+        <v>46080.75</v>
       </c>
     </row>
     <row r="135">
@@ -16445,12 +16445,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16555,7 +16555,7 @@
         <v>0</v>
       </c>
       <c r="AI135" s="3" t="n">
-        <v>46080.70833333334</v>
+        <v>46080.79166666666</v>
       </c>
     </row>
     <row r="136">
@@ -16564,12 +16564,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16674,7 +16674,7 @@
         <v>0</v>
       </c>
       <c r="AI136" s="3" t="n">
-        <v>46080.73958333334</v>
+        <v>46080.79166666666</v>
       </c>
     </row>
     <row r="137">
@@ -16683,7 +16683,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16793,7 +16793,7 @@
         <v>0</v>
       </c>
       <c r="AI137" s="3" t="n">
-        <v>46080.75</v>
+        <v>46080.85416666666</v>
       </c>
     </row>
     <row r="138">
@@ -16802,7 +16802,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16912,7 +16912,7 @@
         <v>0</v>
       </c>
       <c r="AI138" s="3" t="n">
-        <v>46080.75</v>
+        <v>46080.85416666666</v>
       </c>
     </row>
     <row r="139">
@@ -16921,12 +16921,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17031,7 +17031,7 @@
         <v>0</v>
       </c>
       <c r="AI139" s="3" t="n">
-        <v>46080.75</v>
+        <v>46080.875</v>
       </c>
     </row>
     <row r="140">
@@ -17040,12 +17040,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17150,7 +17150,7 @@
         <v>0</v>
       </c>
       <c r="AI140" s="3" t="n">
-        <v>46080.79166666666</v>
+        <v>46080.875</v>
       </c>
     </row>
     <row r="141">
@@ -17159,27 +17159,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17269,7 +17269,7 @@
         <v>0</v>
       </c>
       <c r="AI141" s="3" t="n">
-        <v>46080.79166666666</v>
+        <v>46080.875</v>
       </c>
     </row>
     <row r="142">
@@ -17278,27 +17278,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17388,7 +17388,7 @@
         <v>0</v>
       </c>
       <c r="AI142" s="3" t="n">
-        <v>46080.85416666666</v>
+        <v>46080.875</v>
       </c>
     </row>
     <row r="143">
@@ -17397,27 +17397,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17507,7 +17507,7 @@
         <v>0</v>
       </c>
       <c r="AI143" s="3" t="n">
-        <v>46080.85416666666</v>
+        <v>46080.875</v>
       </c>
     </row>
     <row r="144">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,22 +18711,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19658,27 +19658,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19768,601 +19768,6 @@
         <v>0</v>
       </c>
       <c r="AI162" s="3" t="n">
-        <v>46080.875</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="n">
-        <v>46080</v>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Slovenia PrvaLiga</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Domžale</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Aluminij</t>
-        </is>
-      </c>
-      <c r="G163" t="n">
-        <v>0</v>
-      </c>
-      <c r="H163" t="n">
-        <v>0</v>
-      </c>
-      <c r="I163" t="n">
-        <v>0</v>
-      </c>
-      <c r="J163" t="n">
-        <v>0</v>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>canceled</t>
-        </is>
-      </c>
-      <c r="L163" t="n">
-        <v>0</v>
-      </c>
-      <c r="M163" t="n">
-        <v>0</v>
-      </c>
-      <c r="N163" t="n">
-        <v>0</v>
-      </c>
-      <c r="O163" t="n">
-        <v>0</v>
-      </c>
-      <c r="P163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
-      <c r="R163" t="n">
-        <v>0</v>
-      </c>
-      <c r="S163" t="n">
-        <v>0</v>
-      </c>
-      <c r="T163" t="n">
-        <v>0</v>
-      </c>
-      <c r="U163" t="n">
-        <v>0</v>
-      </c>
-      <c r="V163" t="n">
-        <v>0</v>
-      </c>
-      <c r="W163" t="n">
-        <v>0</v>
-      </c>
-      <c r="X163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI163" s="3" t="n">
-        <v>46080.875</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="n">
-        <v>46080</v>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Dubočica</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Stepojevac Vaga</t>
-        </is>
-      </c>
-      <c r="G164" t="n">
-        <v>0</v>
-      </c>
-      <c r="H164" t="n">
-        <v>0</v>
-      </c>
-      <c r="I164" t="n">
-        <v>0</v>
-      </c>
-      <c r="J164" t="n">
-        <v>0</v>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L164" t="n">
-        <v>0</v>
-      </c>
-      <c r="M164" t="n">
-        <v>0</v>
-      </c>
-      <c r="N164" t="n">
-        <v>0</v>
-      </c>
-      <c r="O164" t="n">
-        <v>0</v>
-      </c>
-      <c r="P164" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
-      <c r="R164" t="n">
-        <v>0</v>
-      </c>
-      <c r="S164" t="n">
-        <v>0</v>
-      </c>
-      <c r="T164" t="n">
-        <v>0</v>
-      </c>
-      <c r="U164" t="n">
-        <v>0</v>
-      </c>
-      <c r="V164" t="n">
-        <v>0</v>
-      </c>
-      <c r="W164" t="n">
-        <v>0</v>
-      </c>
-      <c r="X164" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y164" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI164" s="3" t="n">
-        <v>46080.875</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="n">
-        <v>46080</v>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Borac Banja Luka</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Sarajevo</t>
-        </is>
-      </c>
-      <c r="G165" t="n">
-        <v>0</v>
-      </c>
-      <c r="H165" t="n">
-        <v>0</v>
-      </c>
-      <c r="I165" t="n">
-        <v>0</v>
-      </c>
-      <c r="J165" t="n">
-        <v>0</v>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L165" t="n">
-        <v>0</v>
-      </c>
-      <c r="M165" t="n">
-        <v>0</v>
-      </c>
-      <c r="N165" t="n">
-        <v>0</v>
-      </c>
-      <c r="O165" t="n">
-        <v>0</v>
-      </c>
-      <c r="P165" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
-      <c r="R165" t="n">
-        <v>0</v>
-      </c>
-      <c r="S165" t="n">
-        <v>0</v>
-      </c>
-      <c r="T165" t="n">
-        <v>0</v>
-      </c>
-      <c r="U165" t="n">
-        <v>0</v>
-      </c>
-      <c r="V165" t="n">
-        <v>0</v>
-      </c>
-      <c r="W165" t="n">
-        <v>0</v>
-      </c>
-      <c r="X165" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y165" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI165" s="3" t="n">
-        <v>46080.875</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="n">
-        <v>46080</v>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Voždovac</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="G166" t="n">
-        <v>0</v>
-      </c>
-      <c r="H166" t="n">
-        <v>0</v>
-      </c>
-      <c r="I166" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" t="n">
-        <v>0</v>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L166" t="n">
-        <v>0</v>
-      </c>
-      <c r="M166" t="n">
-        <v>0</v>
-      </c>
-      <c r="N166" t="n">
-        <v>0</v>
-      </c>
-      <c r="O166" t="n">
-        <v>0</v>
-      </c>
-      <c r="P166" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
-      <c r="R166" t="n">
-        <v>0</v>
-      </c>
-      <c r="S166" t="n">
-        <v>0</v>
-      </c>
-      <c r="T166" t="n">
-        <v>0</v>
-      </c>
-      <c r="U166" t="n">
-        <v>0</v>
-      </c>
-      <c r="V166" t="n">
-        <v>0</v>
-      </c>
-      <c r="W166" t="n">
-        <v>0</v>
-      </c>
-      <c r="X166" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y166" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI166" s="3" t="n">
-        <v>46080.875</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="n">
-        <v>46080</v>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Técnico Universitario</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Orense SC</t>
-        </is>
-      </c>
-      <c r="G167" t="n">
-        <v>0</v>
-      </c>
-      <c r="H167" t="n">
-        <v>0</v>
-      </c>
-      <c r="I167" t="n">
-        <v>0</v>
-      </c>
-      <c r="J167" t="n">
-        <v>0</v>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L167" t="n">
-        <v>0</v>
-      </c>
-      <c r="M167" t="n">
-        <v>0</v>
-      </c>
-      <c r="N167" t="n">
-        <v>0</v>
-      </c>
-      <c r="O167" t="n">
-        <v>0</v>
-      </c>
-      <c r="P167" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
-      <c r="R167" t="n">
-        <v>0</v>
-      </c>
-      <c r="S167" t="n">
-        <v>0</v>
-      </c>
-      <c r="T167" t="n">
-        <v>0</v>
-      </c>
-      <c r="U167" t="n">
-        <v>0</v>
-      </c>
-      <c r="V167" t="n">
-        <v>0</v>
-      </c>
-      <c r="W167" t="n">
-        <v>0</v>
-      </c>
-      <c r="X167" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y167" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI167" s="3" t="n">
         <v>46080.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.32</v>
+        <v>3.07</v>
       </c>
       <c r="M62" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N62" t="n">
-        <v>2.72</v>
+        <v>2.16</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,16 +7844,16 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7969,10 +7969,10 @@
         <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,22 +8477,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.89</v>
+        <v>2.82</v>
       </c>
       <c r="M70" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="N70" t="n">
-        <v>3.86</v>
+        <v>2.4</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.6</v>
+        <v>2.01</v>
       </c>
       <c r="M71" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N71" t="n">
-        <v>5.07</v>
+        <v>3.58</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8985,17 +8985,17 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.82</v>
+        <v>1.89</v>
       </c>
       <c r="M76" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="N76" t="n">
-        <v>2.4</v>
+        <v>3.86</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.01</v>
+        <v>1.54</v>
       </c>
       <c r="M78" t="n">
-        <v>3.1</v>
+        <v>3.72</v>
       </c>
       <c r="N78" t="n">
-        <v>3.58</v>
+        <v>5.52</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.56</v>
+        <v>3.03</v>
       </c>
       <c r="M82" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N82" t="n">
-        <v>5.18</v>
+        <v>2.17</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.5</v>
+        <v>1.42</v>
       </c>
       <c r="M112" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N112" t="n">
-        <v>2.5</v>
+        <v>7.09</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.42</v>
+        <v>2.08</v>
       </c>
       <c r="M115" t="n">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="N115" t="n">
-        <v>7.09</v>
+        <v>3.19</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.25</v>
+        <v>3.31</v>
       </c>
       <c r="M116" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="N116" t="n">
-        <v>2.89</v>
+        <v>2.29</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.56</v>
+        <v>1.69</v>
       </c>
       <c r="M117" t="n">
-        <v>3.21</v>
+        <v>3.74</v>
       </c>
       <c r="N117" t="n">
-        <v>2.9</v>
+        <v>4.85</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>3.31</v>
+        <v>2.25</v>
       </c>
       <c r="M118" t="n">
-        <v>3.04</v>
+        <v>3.24</v>
       </c>
       <c r="N118" t="n">
-        <v>2.29</v>
+        <v>2.89</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.69</v>
+        <v>2.56</v>
       </c>
       <c r="M120" t="n">
-        <v>3.74</v>
+        <v>3.21</v>
       </c>
       <c r="N120" t="n">
-        <v>4.85</v>
+        <v>2.9</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,22 +14784,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.08</v>
+        <v>2.7</v>
       </c>
       <c r="M121" t="n">
-        <v>3.28</v>
+        <v>3.66</v>
       </c>
       <c r="N121" t="n">
-        <v>3.19</v>
+        <v>2.7</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.57</v>
+        <v>2.34</v>
       </c>
       <c r="M122" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N122" t="n">
-        <v>4.35</v>
+        <v>2.57</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,22 +15022,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,22 +15260,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,22 +15498,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.32</v>
+        <v>4.62</v>
       </c>
       <c r="M128" t="n">
-        <v>3.5</v>
+        <v>3.84</v>
       </c>
       <c r="N128" t="n">
-        <v>2.85</v>
+        <v>1.86</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,7 +15698,7 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AB128" t="n">
         <v>1.95</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,22 +16212,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,22 +17164,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,22 +17283,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18029,7 +18029,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L158" t="n">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G161" t="n">

--- a/jogos_2026-02-27.xlsx
+++ b/jogos_2026-02-27.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.32</v>
+        <v>2.26</v>
       </c>
       <c r="M21" t="n">
-        <v>2.69</v>
+        <v>3.03</v>
       </c>
       <c r="N21" t="n">
-        <v>2.08</v>
+        <v>3.65</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="M39" t="n">
-        <v>3.74</v>
+        <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,22 +8596,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.82</v>
+        <v>1.54</v>
       </c>
       <c r="M70" t="n">
-        <v>3.3</v>
+        <v>3.72</v>
       </c>
       <c r="N70" t="n">
-        <v>2.4</v>
+        <v>5.52</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="M71" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="N71" t="n">
-        <v>3.58</v>
+        <v>3.27</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.89</v>
+        <v>2.82</v>
       </c>
       <c r="M76" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="N76" t="n">
-        <v>3.86</v>
+        <v>2.4</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="M77" t="n">
-        <v>3.13</v>
+        <v>3.22</v>
       </c>
       <c r="N77" t="n">
-        <v>3.27</v>
+        <v>3.86</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="M83" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N83" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,10 +11488,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.43</v>
+        <v>2.97</v>
       </c>
       <c r="M93" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="N93" t="n">
         <v>2.36</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="M101" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="N101" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>7.09</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13951,22 +13951,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>3.31</v>
+        <v>2.7</v>
       </c>
       <c r="M116" t="n">
-        <v>3.04</v>
+        <v>3.66</v>
       </c>
       <c r="N116" t="n">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.25</v>
+        <v>1.69</v>
       </c>
       <c r="M118" t="n">
-        <v>3.24</v>
+        <v>3.74</v>
       </c>
       <c r="N118" t="n">
-        <v>2.89</v>
+        <v>4.85</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="M120" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="N120" t="n">
-        <v>2.9</v>
+        <v>2.57</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="M121" t="n">
-        <v>3.66</v>
+        <v>3.21</v>
       </c>
       <c r="N121" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="M122" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="N122" t="n">
-        <v>2.57</v>
+        <v>2.89</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>7.09</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.84</v>
+        <v>2.32</v>
       </c>
       <c r="M125" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N125" t="n">
-        <v>4.29</v>
+        <v>2.85</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,22 +15498,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inline